--- a/06_系统管理/配置管理检查表_CM-01~CM-52.xlsx
+++ b/06_系统管理/配置管理检查表_CM-01~CM-52.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置管理检查表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置管理检查表（严格版）" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -41,7 +41,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -66,6 +66,12 @@
         <bgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -85,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +103,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -465,14 +474,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
-    <col width="50" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -493,12 +503,17 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>本项目对应内容/证据</t>
+          <t>本项目实际情况/证据</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
           <t>状态</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>差距说明</t>
         </is>
       </c>
     </row>
@@ -520,12 +535,17 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>配置管理计划于第4周完成（课程任务安排），计划1.1节已注明RUP建议精化阶段初期编写并说明差异；开发计划2.3节将CM计划排在第4周</t>
+          <t>配置管理计划于第4周完成（课程任务安排），开发计划2.3节也排在第4周；RUP讲义建议精化阶段初期（第2-3周）</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
           <t>△</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>时机偏晚1-2周，已在计划1.1节说明差异</t>
         </is>
       </c>
     </row>
@@ -547,12 +567,17 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>计划1.1节明确：每阶段开始前审查，范围/人员/工具变更时更新版本走CR流程</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>计划1.1节已写审查规则，但项目当前仅完成初始和细化阶段，尚未实际执行过阶段审查</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>规则已定，未实际执行过审查</t>
         </is>
       </c>
     </row>
@@ -574,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>配置库已建立，计划存放于06_系统管理/配置管理计划.docx，配置库目录结构见附录A</t>
+          <t>配置库已建立，配置管理计划存放于06_系统管理/，GitHub仓库已推送</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
@@ -582,6 +607,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -609,6 +635,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -636,6 +663,11 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>文档层面覆盖</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -663,6 +695,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -682,7 +715,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>计划2.1节角色与职责表（6人角色+配置管理职责）</t>
+          <t>计划2.1节6人角色与配置管理职责表</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -690,6 +723,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -717,6 +751,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -744,6 +779,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -763,7 +799,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>计划2.2.1节工具环境表（Git/GitHub/Worktile/Draw.io/墨刀/SpringBoot/Vue/MySQL）</t>
+          <t>计划2.2.1节工具环境表；Git v2.46.2已实际安装并加入PATH</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -771,6 +807,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -790,7 +827,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>计划2.2.2节分支策略（main/develop/feature/credit/feature/security）+合并规则</t>
+          <t>计划2.2.2节分支策略；Git仓库已初始化，4个分支已创建并推送GitHub</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -798,6 +835,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -812,7 +850,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>必须回答：①产品数据量预期大小②产品团队分配③服务器和客户机实际位置</t>
+          <t>必须回答：①数据量②团队分配③服务器和客户机位置</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -825,6 +863,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -852,6 +891,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -871,7 +911,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>计划3.1.1节明确覆盖：无自研硬件/JDK/MySQL/COTS(Element-UI/uView/vue-element-admin/MyBatis-Plus)/全部开发工件</t>
+          <t>计划3.1.1节明确覆盖无自研硬件/JDK/MySQL/COTS(Element-UI/uView/vue-element-admin/MyBatis-Plus)/全部开发工件</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -879,6 +919,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -906,6 +947,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -925,12 +967,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>计划3.1.2节+基线清单：5条基线（初始/细化/构建一/构建二/交付），对齐开发计划8个里程碑</t>
+          <t>计划3.1.2节+基线清单：5条基线计划；BL-1（初始阶段）和BL-2（细化阶段）已实际建立并打Git标签</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
           <t>√</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>BL-3/4/5待后续阶段</t>
         </is>
       </c>
     </row>
@@ -952,12 +999,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>计划3.1.2节+启动会决议：配置经理执行→项目经理批准→指导老师确认</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>计划3.1.2节+启动会决议写了"配置经理执行→项目经理批准→指导老师确认"，但实际无正式审批签字记录</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>规则已定，实际审批流程未正式走</t>
         </is>
       </c>
     </row>
@@ -979,7 +1031,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>计划3.1.2节+基线清单.docx：BL-1含开发计划，BL-2含SRS+3份原型+界面说明</t>
+          <t>计划3.1.2节+基线清单.docx：BL-1含开发计划，BL-2含SRS+3份原型+界面说明，均有实际快照文件</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -987,6 +1039,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1006,12 +1059,17 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>计划3.2.1节8步流程+CR变更请求单模板.docx+CR变更台账.xlsx；已注明SRS第8章缺失，变更流程暂由CM计划定义</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>计划3.2.1节8步流程+CR变更请求单模板.docx+CR变更台账.xlsx；但台账仅1行示例，无实际变更记录</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>流程模板已定义，无实际变更记录</t>
         </is>
       </c>
     </row>
@@ -1033,12 +1091,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>计划3.2.2节+启动会决议：主席马明昂，委员宁徽/姜贺添，指导老师审批；高优先级2工作日内评审</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>计划3.2.2节+启动会决议定义了成员（主席马明昂，委员宁徽/姜贺添，指导老师审批），但CCB未实际开过会</t>
+        </is>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>成员已定，未实际运作</t>
         </is>
       </c>
     </row>
@@ -1060,12 +1123,17 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>计划3.2.1节CR表单含"变更影响评估"字段，评估对基线/迭代计划/SRS追踪矩阵影响</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>计划3.2.1节CR表单含"变更影响评估"字段，但无实际评估记录</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>模板有，无实际评估</t>
         </is>
       </c>
     </row>
@@ -1087,12 +1155,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>计划3.2.1节明确：SQL脚本属受控配置项，要求可重复执行+附回滚方案</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>计划3.2.1节写了SQL脚本受控规则，但项目目前无实际SQL脚本入库（SRS有表设计但无sql文件）</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>规则有，无实际脚本纳管</t>
         </is>
       </c>
     </row>
@@ -1109,17 +1182,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>说明保留策略、替代计划、事故处理计划、恢复计划</t>
+          <t>说明保留策略、替代计划、事故处理、恢复计划</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>计划3.3.1节+配置库备份与恢复方案.docx：双副本策略/替代计划/事故处理5步/恢复7步</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>计划3.3.1节+配置库备份与恢复方案.docx；但备份未实际执行过（无实际zip备份包）</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>方案有，未实际执行备份</t>
         </is>
       </c>
     </row>
@@ -1149,6 +1227,11 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>规则已定义</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1163,17 +1246,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>说明发布版内容、针对对象、已知问题、安装说明</t>
+          <t>说明发布版内容、对象、已知问题、安装说明</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>计划3.3.1节4个发布版表（原型演示版/Alpha/Beta/最终演示版），要求写明内容/对象/已知问题/安装说明</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>计划3.3.1节定义了4个发布版（原型演示版/Alpha/Beta/最终演示版）；实际仅完成原型演示版（第3周）</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>规则有，实际仅完成1/4发布</t>
         </is>
       </c>
     </row>
@@ -1195,12 +1283,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>计划3.3.2节+周配置状态报告模板.docx+配置审计检查清单.docx</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>计划3.3.2节+周配置状态报告模板.docx+配置审计检查清单.docx；但无实际周报告和审计记录</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>模板有，未实际执行</t>
         </is>
       </c>
     </row>
@@ -1222,12 +1315,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>计划3.3.2节+缺陷统计报告模板.docx：高/中/低三级分类</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>缺陷统计报告模板.docx有高/中/低三级分类，但无实际缺陷数据</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>模板有，无实际数据</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1347,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>缺陷统计报告模板.docx第二节：平均打开时长/滞后时间/高优先级修复时长</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>缺陷统计报告模板第二节有统计项，但无实际数据</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>模板有，无实际数据</t>
         </is>
       </c>
     </row>
@@ -1276,12 +1379,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>缺陷统计报告模板.docx第三节：按拥有者/优先级/修复状态/模块分布</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>缺陷统计报告模板第三节有统计项，但无实际数据</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>模板有，无实际数据</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1411,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>缺陷统计报告模板.docx第四节：累计发现/修复/频率/质量差距/平均解决时长</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>缺陷统计报告模板第四节有统计项，但无实际数据</t>
+        </is>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>模板有，无实际数据</t>
         </is>
       </c>
     </row>
@@ -1330,7 +1443,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>计划第4章里程碑表，8个里程碑对齐开发计划4.2.1.3，每项标注CM工作内容</t>
+          <t>计划第4章8个里程碑表，对齐开发计划4.2.1.3，每项标注CM工作内容</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
@@ -1338,6 +1451,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1365,6 +1479,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1384,12 +1499,17 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>计划第5章：工具(Git/GitHub/Worktile等)/人员(配置经理1人+全体6人)/培训(第1周Git培训已安排)</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>计划第5章：工具/人员/培训（第1周Git培训已在开发计划中安排）；但无培训记录/考核记录</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>计划有，实际培训执行情况无记录</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1531,17 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>计划第6章：WarmSearch开源基线代码单独存放extern-baseline目录+记录来源许可证；COTS组件锁定版本(Element-UI/uView1.8.2/vue-element-admin4.3.1/MyBatis-Plus)</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>计划第6章写了WarmSearch开源基线管控规则和COTS组件版本锁定；但WarmSearch基线代码实际未放入配置库（02目录仅.gitkeep）</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>规则有，实际基线代码未入库</t>
         </is>
       </c>
     </row>
@@ -1438,7 +1563,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>配置库01_系统需求/：SRS+3份原型+界面说明.pdf</t>
+          <t>配置库01_系统需求/：SRS+3份原型+界面说明.pdf，共5个文件</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -1446,6 +1571,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1465,12 +1591,17 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>配置库02_系统设计与实施/：目录已建，设计文档待后续迭代产出（项目当前第4周）</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>配置库02_系统设计与实施/：仅.gitkeep占位文件，无实际设计文档（设计文档待后续迭代产出）</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>目录已建，内容待产出</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1623,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>配置库03_系统集成/：目录已建，集成计划待构建阶段产出</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>配置库03_系统集成/：仅.gitkeep</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>目录已建，内容待产出</t>
         </is>
       </c>
     </row>
@@ -1519,12 +1655,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>配置库04_系统测试/：目录已建，测试工件待测试经理产出</t>
-        </is>
-      </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>配置库04_系统测试/：仅.gitkeep（测试计划由测试经理负责，当前未产出）</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>目录已建，内容待产出</t>
         </is>
       </c>
     </row>
@@ -1546,12 +1687,17 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>配置库05_系统部署/：目录已建，部署工件待交付阶段产出</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>配置库05_系统部署/：仅.gitkeep</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>目录已建，内容待产出</t>
         </is>
       </c>
     </row>
@@ -1573,7 +1719,7 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>配置库06_系统管理/：开发计划+配置管理计划+启动会决议+CR模板+台账+报告模板+审计清单+备份方案</t>
+          <t>配置库06_系统管理/：开发计划+配置管理计划+启动会决议+CR模板+台账+3个报告模板+审计清单+备份方案+检查表，共11个文件</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -1581,6 +1727,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -1600,12 +1747,17 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>配置库07_工具与标准/：目录已建，工具清单已在计划2.2.1节列明</t>
-        </is>
-      </c>
-      <c r="E42" s="3" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>配置库07_工具与标准/：仅.gitkeep；工具清单已在计划2.2.1节列明但无独立文档</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>目录已建，内容待产出</t>
         </is>
       </c>
     </row>
@@ -1627,12 +1779,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>配置库07_工具与标准/：目录已建，SRS 5.2提到各类指南但文档未提供，待后续产出</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>△</t>
+          <t>配置库07_工具与标准/：仅.gitkeep；SRS 5.2提到各类指南但文档未提供</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>□</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>目录已建，内容待产出</t>
         </is>
       </c>
     </row>
@@ -1662,6 +1819,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F44" s="2" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -1689,6 +1847,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F45" s="2" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -1716,6 +1875,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F46" s="2" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -1735,7 +1895,7 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>计划3.1.1节：BL代表内部基线，#为基线整数编号</t>
+          <t>计划3.1.1节：BL代表内部基线，#为基线整数编号；已实际打WS_BL-1、WS_BL-2标签</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -1743,6 +1903,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F47" s="2" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -1770,6 +1931,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F48" s="2" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -1789,7 +1951,7 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>计划附录B.1+2.2.2节：feature/*=私有开发工作区，develop=集成工作区，6人各分配feature分支</t>
+          <t>计划附录B.1+2.2.2节：feature/*=私有开发工作区，develop=集成工作区；4个分支已实际创建</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
@@ -1797,6 +1959,7 @@
           <t>√</t>
         </is>
       </c>
+      <c r="F49" s="2" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -1816,12 +1979,17 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>计划3.1.2节+附录B：develop→feature/*的rebase/merge规则</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>计划3.1.2节+附录B写了develop→feature/*的rebase/merge规则，但未实际执行过基线调整</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>规则有，未实际执行</t>
         </is>
       </c>
     </row>
@@ -1843,12 +2011,17 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>计划附录B.2：Git合并识别冲突，开发人员协同解决，配置经理监督，评审后并入</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>计划附录B.2写了Git冲突解决规则，但项目未实际遇到并发冲突</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>规则有，未实际执行</t>
         </is>
       </c>
     </row>
@@ -1870,12 +2043,17 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>计划附录B.3：Worktile任务通知+项目组渠道，仅通知相关人员，不全员广播</t>
-        </is>
-      </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>计划附录B.3写了Worktile通知规则，但未实际执行</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>规则有，未实际执行</t>
         </is>
       </c>
     </row>
@@ -1897,34 +2075,39 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>计划附录B.4：4条版本线，缺陷通过CR流程评估影响范围，修复回灌所有受影响版本</t>
-        </is>
-      </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>√</t>
+          <t>计划附录B.4写了4条版本线修复回灌规则，但目前仅一个版本线，无多版本并行</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>△</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>规则有，当前单版本</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="5" t="inlineStr">
+      <c r="A55" s="6" t="inlineStr">
         <is>
           <t>汇总</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>√已完成：45项</t>
+          <t>√实际完成：26项</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>△部分完成：7项</t>
+          <t>△规则/模板已定义但未实际执行：20项</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>□未完成：0项</t>
+          <t>□未完成（目录已建内容待产出）：6项</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
